--- a/inasistencias-4b-ElectYsistDeComTP/alumnos-4b-ElectroYSistDeCom.xlsx
+++ b/inasistencias-4b-ElectYsistDeComTP/alumnos-4b-ElectroYSistDeCom.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="88">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -35,9 +35,6 @@
     <t xml:space="preserve">Grupos</t>
   </si>
   <si>
-    <t xml:space="preserve">Grupo</t>
-  </si>
-  <si>
     <t xml:space="preserve">obs</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
     <t xml:space="preserve">1-Hidroelectrica</t>
   </si>
   <si>
-    <t xml:space="preserve">1-hidroejectrica</t>
-  </si>
-  <si>
     <t xml:space="preserve">P</t>
   </si>
   <si>
@@ -77,7 +71,10 @@
     <t xml:space="preserve">no trajo, traer prototipo según el digubjo, con ladron de joules</t>
   </si>
   <si>
-    <t xml:space="preserve">circuito soldado y andando</t>
+    <t xml:space="preserve">ladron de joules completo y andando y andando y soldado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arreglar el ladron de joules, soldar el capacitor, colocar todo en cajita y probar en clase la parte</t>
   </si>
   <si>
     <t xml:space="preserve">Eugenia</t>
@@ -101,81 +98,90 @@
     <t xml:space="preserve">LAGOS</t>
   </si>
   <si>
+    <t xml:space="preserve">Benicio Valentin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUNA SERRANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se vio en cuaderno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TISEYRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zaira Ruth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chucusea Quiroga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-biomasa y eolica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">descompuesta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">van a traer las boterras, fotos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no tenemos nada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tienen que traer un informe, fotos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soldar los componentes , todo unto en una cajita. llevar el modelo al video, si funciona mantenemos el 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julieta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGUEZ MIÑO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piden cambiar a energia eolica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Emanuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUÁREZ CESPEDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santino Jonas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORREA</t>
+  </si>
+  <si>
     <t xml:space="preserve">3-solar</t>
   </si>
   <si>
-    <t xml:space="preserve">Benicio Valentin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUNA SERRANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4-pila de magnesion y cobre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se vio en cuaderno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicolás</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TISEYRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-pizo electrico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zaira Ruth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chucusea Quiroga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-biomasa y eolica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">descompuesta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">van a traer las boterras, fotos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julieta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODRIGUEZ MIÑO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piden cambiar a energia eolica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Emanuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUÁREZ CESPEDES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santino Jonas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORREA</t>
-  </si>
-  <si>
     <t xml:space="preserve">traer panel solar , bateria de plomo</t>
   </si>
   <si>
     <t xml:space="preserve">no trajeron foto, para la proxima</t>
   </si>
   <si>
+    <t xml:space="preserve">trajeron panel, controlaor, bateria, cables</t>
+  </si>
+  <si>
     <t xml:space="preserve">Farid Emir</t>
   </si>
   <si>
     <t xml:space="preserve">PEREYRA</t>
   </si>
   <si>
+    <t xml:space="preserve">conseguir manual, formas de conexión</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tobías Valentín</t>
   </si>
   <si>
@@ -200,6 +206,9 @@
     <t xml:space="preserve"> traer el material, para mostrar funcionamiento x3</t>
   </si>
   <si>
+    <t xml:space="preserve">armar un ladron de joules y por lo menos 3 tapers conectados en serie</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paloma Marianella</t>
   </si>
   <si>
@@ -237,9 +246,6 @@
   </si>
   <si>
     <t xml:space="preserve">GOMEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3-biomasa y eolica</t>
   </si>
   <si>
     <t xml:space="preserve">Mateo Bautista</t>
@@ -290,7 +296,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -311,6 +317,12 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="0"/>
     </font>
   </fonts>
@@ -362,7 +374,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -371,11 +383,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -395,6 +407,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -404,7 +424,46 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFFCC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF006600"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -683,16 +742,20 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31.19"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="24.5"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="8.62"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="12" min="7" style="1" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="13.32"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="22" min="14" style="1" width="8.79"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="23" min="23" style="0" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="63.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="53.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="63.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16326" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.62"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="6" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.32"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="13" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="63.84"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="25" min="24" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="53.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="27" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="63.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="60.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="81.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16327" min="16327" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16328" min="16328" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16329" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -708,331 +771,369 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="n">
-        <v>46093</v>
-      </c>
-      <c r="G1" s="3" t="n">
-        <v>46108</v>
-      </c>
-      <c r="H1" s="3" t="n">
-        <v>46122</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3" t="n">
-        <v>46129</v>
-      </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3" t="n">
-        <v>46136</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="N1" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="O1" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="P1" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="3" t="n">
-        <v>46150</v>
-      </c>
-      <c r="O1" s="3" t="n">
-        <v>46157</v>
-      </c>
-      <c r="P1" s="3" t="n">
-        <v>46164</v>
-      </c>
-      <c r="Q1" s="3" t="n">
-        <v>46171</v>
-      </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="W1" s="3" t="n">
+      <c r="U1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V1" s="2" t="n">
         <v>46178</v>
       </c>
-      <c r="X1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y1" s="3" t="n">
+      <c r="W1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="X1" s="2" t="n">
         <v>46185</v>
       </c>
-      <c r="Z1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB1" s="3" t="n">
+      <c r="Y1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA1" s="2" t="n">
         <v>46192</v>
       </c>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE1" s="3" t="n">
+      <c r="AB1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD1" s="2" t="n">
         <v>46199</v>
       </c>
-      <c r="AF1" s="3" t="n">
-        <v>46206</v>
-      </c>
-      <c r="AG1" s="3" t="n">
-        <v>46213</v>
-      </c>
-      <c r="AH1" s="3" t="n">
+      <c r="AE1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG1" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="AI1" s="3" t="n">
+      <c r="AH1" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ1" s="2" t="n">
         <v>46227</v>
       </c>
-      <c r="AJ1" s="3" t="n">
+      <c r="AK1" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="AK1" s="3" t="n">
+      <c r="AL1" s="2" t="n">
         <v>46241</v>
       </c>
-      <c r="AL1" s="3" t="n">
+      <c r="AM1" s="2" t="n">
         <v>46248</v>
       </c>
-      <c r="AM1" s="3" t="n">
+      <c r="AN1" s="2" t="n">
         <v>46255</v>
       </c>
-      <c r="AN1" s="3" t="n">
+      <c r="AO1" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="AO1" s="3" t="n">
+      <c r="AP1" s="2" t="n">
         <v>46269</v>
       </c>
-      <c r="AP1" s="3" t="n">
+      <c r="AQ1" s="2" t="n">
         <v>46276</v>
       </c>
-      <c r="AQ1" s="3" t="n">
+      <c r="AR1" s="2" t="n">
         <v>46283</v>
       </c>
-      <c r="AR1" s="3" t="n">
+      <c r="AS1" s="2" t="n">
         <v>46290</v>
       </c>
-      <c r="AS1" s="3" t="n">
+      <c r="AT1" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="AT1" s="3" t="n">
+      <c r="AU1" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="AU1" s="3" t="n">
+      <c r="AV1" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="AV1" s="3" t="n">
+      <c r="AW1" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="AW1" s="3" t="n">
+      <c r="AX1" s="2" t="n">
         <v>46325</v>
       </c>
-      <c r="AX1" s="3" t="n">
+      <c r="AY1" s="2" t="n">
         <v>46332</v>
       </c>
-      <c r="AY1" s="3" t="n">
+      <c r="AZ1" s="2" t="n">
         <v>46339</v>
       </c>
-      <c r="AZ1" s="3" t="n">
+      <c r="BA1" s="2" t="n">
         <v>46346</v>
       </c>
-      <c r="BA1" s="3" t="n">
+      <c r="BB1" s="2" t="n">
         <v>46353</v>
       </c>
-      <c r="BB1" s="3" t="n">
+      <c r="BC1" s="2" t="n">
         <v>46360</v>
       </c>
-      <c r="BC1" s="3" t="n">
+      <c r="BD1" s="2" t="n">
         <v>46367</v>
       </c>
-      <c r="BD1" s="3" t="n">
+      <c r="BE1" s="2" t="n">
         <v>46374</v>
       </c>
-      <c r="BE1" s="3" t="n">
+      <c r="BF1" s="2" t="n">
         <v>46381</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <f aca="false">COUNTIF(E2:P2,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <f aca="false">COUNTIF(E2:P2,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <f aca="false">SUM(Q2:R2)</f>
+        <v>9</v>
+      </c>
+      <c r="T2" s="4" t="n">
+        <f aca="false">ROUND(Q2*10/S2,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U2" s="1" t="str">
+        <f aca="false">IF(T2&gt;6,"TEA",IF(T2&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="X2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <f aca="false">COUNTIF(F2:Q2,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <f aca="false">COUNTIF(F2:Q2,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <f aca="false">SUM(R2:S2)</f>
-        <v>9</v>
-      </c>
-      <c r="U2" s="4" t="n">
-        <f aca="false">ROUND(R2*10/T2,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V2" s="4" t="str">
-        <f aca="false">IF(U2&gt;6,"TEA",IF(U2&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="X2" s="2" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB2" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z2" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AD2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE2" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI2" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AB2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC2" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="BF2" s="3"/>
-      <c r="BG2" s="3"/>
-      <c r="BH2" s="3"/>
-    </row>
-    <row r="3" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BG2" s="2"/>
+      <c r="BH2" s="2"/>
+      <c r="BI2" s="2"/>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <f aca="false">COUNTIF(F3:Q3,"P")</f>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <f aca="false">COUNTIF(E3:P3,"P")</f>
         <v>8</v>
       </c>
-      <c r="S3" s="2" t="n">
-        <f aca="false">COUNTIF(F3:Q3,"A")</f>
+      <c r="R3" s="3" t="n">
+        <f aca="false">COUNTIF(E3:P3,"A")</f>
         <v>1</v>
       </c>
-      <c r="T3" s="2" t="n">
-        <f aca="false">SUM(R3:S3)</f>
-        <v>9</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <f aca="false">ROUND(R3*10/T3,0)</f>
-        <v>9</v>
-      </c>
-      <c r="V3" s="4" t="str">
-        <f aca="false">IF(U3&gt;6,"TEA",IF(U3&gt;3,"TEP","TED"))</f>
+      <c r="S3" s="3" t="n">
+        <f aca="false">SUM(Q3:R3)</f>
+        <v>9</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <f aca="false">ROUND(Q3*10/S3,0)</f>
+        <v>9</v>
+      </c>
+      <c r="U3" s="1" t="str">
+        <f aca="false">IF(T3&gt;6,"TEA",IF(T3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="XCX3" s="1"/>
+      <c r="V3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE3" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="XCY3" s="1"/>
-      <c r="XCZ3" s="1"/>
+      <c r="XCZ3" s="0"/>
       <c r="XDA3" s="1"/>
       <c r="XDB3" s="1"/>
       <c r="XDC3" s="1"/>
@@ -1090,84 +1191,99 @@
       <c r="XFC3" s="1"/>
       <c r="XFD3" s="1"/>
     </row>
-    <row r="4" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <f aca="false">COUNTIF(F4:Q4,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <f aca="false">COUNTIF(F4:Q4,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <f aca="false">COUNTIF(E4:P4,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <f aca="false">COUNTIF(E4:P4,"A")</f>
         <v>0</v>
       </c>
-      <c r="T4" s="2" t="n">
-        <f aca="false">SUM(R4:S4)</f>
-        <v>9</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <f aca="false">ROUND(R4*10/T4,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V4" s="4" t="str">
-        <f aca="false">IF(U4&gt;6,"TEA",IF(U4&gt;3,"TEP","TED"))</f>
+      <c r="S4" s="3" t="n">
+        <f aca="false">SUM(Q4:R4)</f>
+        <v>9</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <f aca="false">ROUND(Q4*10/S4,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U4" s="1" t="str">
+        <f aca="false">IF(T4&gt;6,"TEA",IF(T4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="XCX4" s="1"/>
+      <c r="V4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="XCY4" s="1"/>
-      <c r="XCZ4" s="1"/>
+      <c r="XCZ4" s="0"/>
       <c r="XDA4" s="1"/>
       <c r="XDB4" s="1"/>
       <c r="XDC4" s="1"/>
@@ -1230,324 +1346,391 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <f aca="false">COUNTIF(F5:Q5,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <f aca="false">COUNTIF(F5:Q5,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <f aca="false">COUNTIF(E5:P5,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <f aca="false">COUNTIF(E5:P5,"A")</f>
         <v>0</v>
       </c>
-      <c r="T5" s="2" t="n">
-        <f aca="false">SUM(R5:S5)</f>
-        <v>9</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <f aca="false">ROUND(R5*10/T5,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V5" s="4" t="str">
-        <f aca="false">IF(U5&gt;6,"TEA",IF(U5&gt;3,"TEP","TED"))</f>
+      <c r="S5" s="3" t="n">
+        <f aca="false">SUM(Q5:R5)</f>
+        <v>9</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <f aca="false">ROUND(Q5*10/S5,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U5" s="1" t="str">
+        <f aca="false">IF(T5&gt;6,"TEA",IF(T5&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z5" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB5" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="V5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="XCZ5" s="0"/>
     </row>
     <row r="6" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="I6" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="N6" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <f aca="false">COUNTIF(F6:Q6,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <f aca="false">COUNTIF(E6:P6,"P")</f>
         <v>7</v>
       </c>
-      <c r="S6" s="7" t="n">
-        <f aca="false">COUNTIF(F6:Q6,"A")</f>
+      <c r="R6" s="7" t="n">
+        <f aca="false">COUNTIF(E6:P6,"A")</f>
         <v>2</v>
       </c>
-      <c r="T6" s="6" t="n">
-        <f aca="false">SUM(R6:S6)</f>
-        <v>9</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <f aca="false">ROUND(R6*10/T6,0)</f>
+      <c r="S6" s="6" t="n">
+        <f aca="false">SUM(Q6:R6)</f>
+        <v>9</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <f aca="false">ROUND(Q6*10/S6,0)</f>
         <v>8</v>
       </c>
-      <c r="V6" s="4" t="str">
-        <f aca="false">IF(U6&gt;6,"TEA",IF(U6&gt;3,"TEP","TED"))</f>
+      <c r="U6" s="1" t="str">
+        <f aca="false">IF(T6&gt;6,"TEA",IF(T6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="X6" s="0"/>
-      <c r="Y6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z6" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB6" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="V6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="XCZ6" s="0"/>
     </row>
     <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>12</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <f aca="false">COUNTIF(F7:Q7,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <f aca="false">COUNTIF(F7:Q7,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <f aca="false">COUNTIF(E7:P7,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <f aca="false">COUNTIF(E7:P7,"A")</f>
         <v>0</v>
       </c>
-      <c r="T7" s="2" t="n">
-        <f aca="false">SUM(R7:S7)</f>
-        <v>9</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <f aca="false">ROUND(R7*10/T7,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V7" s="4" t="str">
-        <f aca="false">IF(U7&gt;6,"TEA",IF(U7&gt;3,"TEP","TED"))</f>
+      <c r="S7" s="3" t="n">
+        <f aca="false">SUM(Q7:R7)</f>
+        <v>9</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <f aca="false">ROUND(Q7*10/S7,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U7" s="1" t="str">
+        <f aca="false">IF(T7&gt;6,"TEA",IF(T7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z7" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="V7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE7" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="XCZ7" s="0"/>
+    </row>
+    <row r="8" s="3" customFormat="true" ht="33.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <f aca="false">COUNTIF(E8:P8,"P")</f>
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <f aca="false">COUNTIF(E8:P8,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <f aca="false">SUM(Q8:R8)</f>
+        <v>9</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <f aca="false">ROUND(Q8*10/S8,0)</f>
+        <v>9</v>
+      </c>
+      <c r="U8" s="1" t="str">
+        <f aca="false">IF(T8&gt;6,"TEA",IF(T8&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="X8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="AA8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="2" t="s">
+      <c r="AG8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R8" s="2" t="n">
-        <f aca="false">COUNTIF(F8:Q8,"P")</f>
-        <v>8</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <f aca="false">COUNTIF(F8:Q8,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="T8" s="2" t="n">
-        <f aca="false">SUM(R8:S8)</f>
-        <v>9</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <f aca="false">ROUND(R8*10/T8,0)</f>
-        <v>9</v>
-      </c>
-      <c r="V8" s="4" t="str">
-        <f aca="false">IF(U8&gt;6,"TEA",IF(U8&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="XCX8" s="1"/>
       <c r="XCY8" s="1"/>
-      <c r="XCZ8" s="1"/>
+      <c r="XCZ8" s="0"/>
       <c r="XDA8" s="1"/>
       <c r="XDB8" s="1"/>
       <c r="XDC8" s="1"/>
@@ -1605,93 +1788,105 @@
       <c r="XFC8" s="1"/>
       <c r="XFD8" s="1"/>
     </row>
-    <row r="9" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P9" s="2" t="s">
+      <c r="P9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <f aca="false">COUNTIF(E9:P9,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <f aca="false">COUNTIF(E9:P9,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <f aca="false">SUM(Q9:R9)</f>
+        <v>9</v>
+      </c>
+      <c r="T9" s="4" t="n">
+        <f aca="false">ROUND(Q9*10/S9,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U9" s="1" t="str">
+        <f aca="false">IF(T9&gt;6,"TEA",IF(T9&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <f aca="false">COUNTIF(F9:Q9,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <f aca="false">COUNTIF(F9:Q9,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="T9" s="2" t="n">
-        <f aca="false">SUM(R9:S9)</f>
-        <v>9</v>
-      </c>
-      <c r="U9" s="4" t="n">
-        <f aca="false">ROUND(R9*10/T9,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V9" s="4" t="str">
-        <f aca="false">IF(U9&gt;6,"TEA",IF(U9&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z9" s="2" t="n">
+      <c r="AD9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AA9" s="0"/>
-      <c r="AB9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="XCX9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI9" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="XCY9" s="1"/>
-      <c r="XCZ9" s="1"/>
+      <c r="XCZ9" s="0"/>
       <c r="XDA9" s="1"/>
       <c r="XDB9" s="1"/>
       <c r="XDC9" s="1"/>
@@ -1749,88 +1944,100 @@
       <c r="XFC9" s="1"/>
       <c r="XFD9" s="1"/>
     </row>
-    <row r="10" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R10" s="2" t="n">
-        <f aca="false">COUNTIF(F10:Q10,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <f aca="false">COUNTIF(E10:P10,"P")</f>
         <v>8</v>
       </c>
-      <c r="S10" s="2" t="n">
-        <f aca="false">COUNTIF(F10:Q10,"A")</f>
+      <c r="R10" s="3" t="n">
+        <f aca="false">COUNTIF(E10:P10,"A")</f>
         <v>1</v>
       </c>
-      <c r="T10" s="2" t="n">
-        <f aca="false">SUM(R10:S10)</f>
-        <v>9</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <f aca="false">ROUND(R10*10/T10,0)</f>
-        <v>9</v>
-      </c>
-      <c r="V10" s="4" t="str">
-        <f aca="false">IF(U10&gt;6,"TEA",IF(U10&gt;3,"TEP","TED"))</f>
+      <c r="S10" s="3" t="n">
+        <f aca="false">SUM(Q10:R10)</f>
+        <v>9</v>
+      </c>
+      <c r="T10" s="4" t="n">
+        <f aca="false">ROUND(Q10*10/S10,0)</f>
+        <v>9</v>
+      </c>
+      <c r="U10" s="1" t="str">
+        <f aca="false">IF(T10&gt;6,"TEA",IF(T10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z10" s="2" t="n">
+      <c r="V10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AB10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC10" s="2" t="n">
+      <c r="AA10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="XCX10" s="1"/>
+      <c r="AD10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="XCY10" s="1"/>
-      <c r="XCZ10" s="1"/>
+      <c r="XCZ10" s="0"/>
       <c r="XDA10" s="1"/>
       <c r="XDB10" s="1"/>
       <c r="XDC10" s="1"/>
@@ -1888,343 +2095,408 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" s="1" customFormat="true" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R11" s="2" t="n">
-        <f aca="false">COUNTIF(F11:Q11,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <f aca="false">COUNTIF(E11:P11,"P")</f>
         <v>8</v>
       </c>
-      <c r="S11" s="2" t="n">
-        <f aca="false">COUNTIF(F11:Q11,"A")</f>
+      <c r="R11" s="3" t="n">
+        <f aca="false">COUNTIF(E11:P11,"A")</f>
         <v>1</v>
       </c>
-      <c r="T11" s="2" t="n">
-        <f aca="false">SUM(R11:S11)</f>
-        <v>9</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <f aca="false">ROUND(R11*10/T11,0)</f>
-        <v>9</v>
-      </c>
-      <c r="V11" s="4" t="str">
-        <f aca="false">IF(U11&gt;6,"TEA",IF(U11&gt;3,"TEP","TED"))</f>
+      <c r="S11" s="3" t="n">
+        <f aca="false">SUM(Q11:R11)</f>
+        <v>9</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <f aca="false">ROUND(Q11*10/S11,0)</f>
+        <v>9</v>
+      </c>
+      <c r="U11" s="1" t="str">
+        <f aca="false">IF(T11&gt;6,"TEA",IF(T11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="V11" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="W11" s="1" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z11" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y11" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AA11" s="2" t="s">
+      <c r="Z11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AB11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="1" t="n">
+      <c r="AA11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB11" s="1" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AD11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="XCZ11" s="0"/>
+    </row>
+    <row r="12" s="1" customFormat="true" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R12" s="2" t="n">
-        <f aca="false">COUNTIF(F12:Q12,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S12" s="2" t="n">
-        <f aca="false">COUNTIF(F12:Q12,"A")</f>
+        <v>46</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <f aca="false">COUNTIF(E12:P12,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <f aca="false">COUNTIF(E12:P12,"A")</f>
         <v>0</v>
       </c>
-      <c r="T12" s="2" t="n">
-        <f aca="false">SUM(R12:S12)</f>
-        <v>9</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <f aca="false">ROUND(R12*10/T12,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V12" s="4" t="str">
-        <f aca="false">IF(U12&gt;6,"TEA",IF(U12&gt;3,"TEP","TED"))</f>
+      <c r="S12" s="3" t="n">
+        <f aca="false">SUM(Q12:R12)</f>
+        <v>9</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <f aca="false">ROUND(Q12*10/S12,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U12" s="1" t="str">
+        <f aca="false">IF(T12&gt;6,"TEA",IF(T12&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z12" s="1" t="n">
+      <c r="V12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC12" s="1" t="n">
+      <c r="AA12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB12" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="AD12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="XCZ12" s="0"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>33</v>
+        <v>46</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R13" s="2" t="n">
-        <f aca="false">COUNTIF(F13:Q13,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S13" s="2" t="n">
-        <f aca="false">COUNTIF(F13:Q13,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <f aca="false">COUNTIF(E13:P13,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <f aca="false">COUNTIF(E13:P13,"A")</f>
         <v>0</v>
       </c>
-      <c r="T13" s="2" t="n">
-        <f aca="false">SUM(R13:S13)</f>
-        <v>9</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <f aca="false">ROUND(R13*10/T13,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V13" s="4" t="str">
-        <f aca="false">IF(U13&gt;6,"TEA",IF(U13&gt;3,"TEP","TED"))</f>
+      <c r="S13" s="3" t="n">
+        <f aca="false">SUM(Q13:R13)</f>
+        <v>9</v>
+      </c>
+      <c r="T13" s="4" t="n">
+        <f aca="false">ROUND(Q13*10/S13,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U13" s="1" t="str">
+        <f aca="false">IF(T13&gt;6,"TEA",IF(T13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z13" s="1" t="n">
+      <c r="V13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC13" s="1" t="n">
+      <c r="AA13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB13" s="1" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AD13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="XCZ13" s="0"/>
+    </row>
+    <row r="14" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>14</v>
+        <v>58</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M14" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N14" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R14" s="2" t="n">
-        <f aca="false">COUNTIF(F14:Q14,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <f aca="false">COUNTIF(E14:P14,"P")</f>
         <v>7</v>
       </c>
-      <c r="S14" s="2" t="n">
-        <f aca="false">COUNTIF(F14:Q14,"A")</f>
+      <c r="R14" s="3" t="n">
+        <f aca="false">COUNTIF(E14:P14,"A")</f>
         <v>2</v>
       </c>
-      <c r="T14" s="2" t="n">
-        <f aca="false">SUM(R14:S14)</f>
-        <v>9</v>
-      </c>
-      <c r="U14" s="4" t="n">
-        <f aca="false">ROUND(R14*10/T14,0)</f>
+      <c r="S14" s="3" t="n">
+        <f aca="false">SUM(Q14:R14)</f>
+        <v>9</v>
+      </c>
+      <c r="T14" s="4" t="n">
+        <f aca="false">ROUND(Q14*10/S14,0)</f>
         <v>8</v>
       </c>
-      <c r="V14" s="4" t="str">
-        <f aca="false">IF(U14&gt;6,"TEA",IF(U14&gt;3,"TEP","TED"))</f>
+      <c r="U14" s="1" t="str">
+        <f aca="false">IF(T14&gt;6,"TEA",IF(T14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="X14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z14" s="2" t="n">
+      <c r="V14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y14" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AA14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC14" s="2" t="n">
+      <c r="Z14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB14" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AD14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="XCX14" s="1"/>
-      <c r="XCY14" s="6"/>
-      <c r="XCZ14" s="6"/>
+      <c r="AC14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="XCY14" s="1"/>
+      <c r="XCZ14" s="0"/>
       <c r="XDA14" s="6"/>
       <c r="XDB14" s="6"/>
       <c r="XDC14" s="6"/>
@@ -2287,85 +2559,97 @@
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>14</v>
+        <v>58</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R15" s="2" t="n">
-        <f aca="false">COUNTIF(F15:Q15,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S15" s="2" t="n">
-        <f aca="false">COUNTIF(F15:Q15,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <f aca="false">COUNTIF(E15:P15,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <f aca="false">COUNTIF(E15:P15,"A")</f>
         <v>0</v>
       </c>
-      <c r="T15" s="2" t="n">
-        <f aca="false">SUM(R15:S15)</f>
-        <v>9</v>
-      </c>
-      <c r="U15" s="4" t="n">
-        <f aca="false">ROUND(R15*10/T15,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V15" s="4" t="str">
-        <f aca="false">IF(U15&gt;6,"TEA",IF(U15&gt;3,"TEP","TED"))</f>
+      <c r="S15" s="3" t="n">
+        <f aca="false">SUM(Q15:R15)</f>
+        <v>9</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <f aca="false">ROUND(Q15*10/S15,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U15" s="1" t="str">
+        <f aca="false">IF(T15&gt;6,"TEA",IF(T15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z15" s="7" t="n">
+      <c r="V15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="X15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AB15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC15" s="7" t="n">
+      <c r="AA15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="XCX15" s="1"/>
+      <c r="AD15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF15" s="1"/>
+      <c r="AG15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI15" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="XCY15" s="1"/>
-      <c r="XCZ15" s="1"/>
+      <c r="XCZ15" s="0"/>
       <c r="XDA15" s="1"/>
       <c r="XDB15" s="1"/>
       <c r="XDC15" s="1"/>
@@ -2423,88 +2707,100 @@
       <c r="XFC15" s="1"/>
       <c r="XFD15" s="1"/>
     </row>
-    <row r="16" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>36</v>
+        <v>58</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R16" s="2" t="n">
-        <f aca="false">COUNTIF(F16:Q16,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <f aca="false">COUNTIF(E16:P16,"P")</f>
         <v>8</v>
       </c>
-      <c r="S16" s="2" t="n">
-        <f aca="false">COUNTIF(F16:Q16,"A")</f>
+      <c r="R16" s="3" t="n">
+        <f aca="false">COUNTIF(E16:P16,"A")</f>
         <v>1</v>
       </c>
-      <c r="T16" s="2" t="n">
-        <f aca="false">SUM(R16:S16)</f>
-        <v>9</v>
-      </c>
-      <c r="U16" s="4" t="n">
-        <f aca="false">ROUND(R16*10/T16,0)</f>
-        <v>9</v>
-      </c>
-      <c r="V16" s="4" t="str">
-        <f aca="false">IF(U16&gt;6,"TEA",IF(U16&gt;3,"TEP","TED"))</f>
+      <c r="S16" s="3" t="n">
+        <f aca="false">SUM(Q16:R16)</f>
+        <v>9</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <f aca="false">ROUND(Q16*10/S16,0)</f>
+        <v>9</v>
+      </c>
+      <c r="U16" s="1" t="str">
+        <f aca="false">IF(T16&gt;6,"TEA",IF(T16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="X16" s="0"/>
-      <c r="Y16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z16" s="2" t="n">
+      <c r="V16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="W16" s="1"/>
+      <c r="X16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y16" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AB16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC16" s="2" t="n">
+      <c r="AA16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB16" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="XCX16" s="1"/>
+      <c r="AD16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE16" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF16" s="1"/>
+      <c r="AG16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="XCY16" s="1"/>
-      <c r="XCZ16" s="1"/>
+      <c r="XCZ16" s="0"/>
       <c r="XDA16" s="1"/>
       <c r="XDB16" s="1"/>
       <c r="XDC16" s="1"/>
@@ -2562,88 +2858,100 @@
       <c r="XFC16" s="1"/>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M17" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="N17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R17" s="2" t="n">
-        <f aca="false">COUNTIF(F17:Q17,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S17" s="2" t="n">
-        <f aca="false">COUNTIF(F17:Q17,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <f aca="false">COUNTIF(E17:P17,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <f aca="false">COUNTIF(E17:P17,"A")</f>
         <v>0</v>
       </c>
-      <c r="T17" s="2" t="n">
-        <f aca="false">SUM(R17:S17)</f>
-        <v>9</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <f aca="false">ROUND(R17*10/T17,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V17" s="4" t="str">
-        <f aca="false">IF(U17&gt;6,"TEA",IF(U17&gt;3,"TEP","TED"))</f>
+      <c r="S17" s="3" t="n">
+        <f aca="false">SUM(Q17:R17)</f>
+        <v>9</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <f aca="false">ROUND(Q17*10/S17,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U17" s="1" t="str">
+        <f aca="false">IF(T17&gt;6,"TEA",IF(T17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z17" s="2" t="n">
+      <c r="V17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y17" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AB17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC17" s="2" t="n">
+      <c r="AA17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB17" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="XCX17" s="1"/>
+      <c r="AD17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="XCY17" s="1"/>
-      <c r="XCZ17" s="1"/>
+      <c r="XCZ17" s="0"/>
       <c r="XDA17" s="1"/>
       <c r="XDB17" s="1"/>
       <c r="XDC17" s="1"/>
@@ -2706,337 +3014,401 @@
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>36</v>
+        <v>70</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R18" s="2" t="n">
-        <f aca="false">COUNTIF(F18:Q18,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S18" s="2" t="n">
-        <f aca="false">COUNTIF(F18:Q18,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <f aca="false">COUNTIF(E18:P18,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <f aca="false">COUNTIF(E18:P18,"A")</f>
         <v>0</v>
       </c>
-      <c r="T18" s="2" t="n">
-        <f aca="false">SUM(R18:S18)</f>
-        <v>9</v>
-      </c>
-      <c r="U18" s="4" t="n">
-        <f aca="false">ROUND(R18*10/T18,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V18" s="4" t="str">
-        <f aca="false">IF(U18&gt;6,"TEA",IF(U18&gt;3,"TEP","TED"))</f>
+      <c r="S18" s="3" t="n">
+        <f aca="false">SUM(Q18:R18)</f>
+        <v>9</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <f aca="false">ROUND(Q18*10/S18,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U18" s="1" t="str">
+        <f aca="false">IF(T18&gt;6,"TEA",IF(T18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z18" s="1" t="n">
+      <c r="V18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y18" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="Z18" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="AA18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="AB18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC18" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AD18" s="2" t="s">
-        <v>68</v>
-      </c>
+      <c r="AC18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE18" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF18" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="XCZ18" s="0"/>
     </row>
     <row r="19" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>72</v>
+      <c r="E19" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R19" s="2" t="n">
-        <f aca="false">COUNTIF(F19:Q19,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <f aca="false">COUNTIF(E19:P19,"P")</f>
         <v>8</v>
       </c>
-      <c r="S19" s="2" t="n">
-        <f aca="false">COUNTIF(F19:Q19,"A")</f>
+      <c r="R19" s="3" t="n">
+        <f aca="false">COUNTIF(E19:P19,"A")</f>
         <v>1</v>
       </c>
-      <c r="T19" s="2" t="n">
-        <f aca="false">SUM(R19:S19)</f>
-        <v>9</v>
-      </c>
-      <c r="U19" s="4" t="n">
-        <f aca="false">ROUND(R19*10/T19,0)</f>
-        <v>9</v>
-      </c>
-      <c r="V19" s="4" t="str">
-        <f aca="false">IF(U19&gt;6,"TEA",IF(U19&gt;3,"TEP","TED"))</f>
+      <c r="S19" s="3" t="n">
+        <f aca="false">SUM(Q19:R19)</f>
+        <v>9</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <f aca="false">ROUND(Q19*10/S19,0)</f>
+        <v>9</v>
+      </c>
+      <c r="U19" s="1" t="str">
+        <f aca="false">IF(T19&gt;6,"TEA",IF(T19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z19" s="1" t="n">
+      <c r="V19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC19" s="1" t="n">
+      <c r="AA19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB19" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="AD19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE19" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="XCZ19" s="0"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>70</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R20" s="2" t="n">
-        <f aca="false">COUNTIF(F20:Q20,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S20" s="2" t="n">
-        <f aca="false">COUNTIF(F20:Q20,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <f aca="false">COUNTIF(E20:P20,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <f aca="false">COUNTIF(E20:P20,"A")</f>
         <v>0</v>
       </c>
-      <c r="T20" s="2" t="n">
-        <f aca="false">SUM(R20:S20)</f>
-        <v>9</v>
-      </c>
-      <c r="U20" s="4" t="n">
-        <f aca="false">ROUND(R20*10/T20,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V20" s="4" t="str">
-        <f aca="false">IF(U20&gt;6,"TEA",IF(U20&gt;3,"TEP","TED"))</f>
+      <c r="S20" s="3" t="n">
+        <f aca="false">SUM(Q20:R20)</f>
+        <v>9</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <f aca="false">ROUND(Q20*10/S20,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U20" s="1" t="str">
+        <f aca="false">IF(T20&gt;6,"TEA",IF(T20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z20" s="1" t="n">
+      <c r="V20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC20" s="1" t="n">
+      <c r="AA20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB20" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="AD20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE20" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="XCZ20" s="0"/>
     </row>
     <row r="21" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>33</v>
+        <v>70</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R21" s="2" t="n">
-        <f aca="false">COUNTIF(F21:Q21,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="S21" s="2" t="n">
-        <f aca="false">COUNTIF(F21:Q21,"A")</f>
+        <v>13</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <f aca="false">COUNTIF(E21:P21,"P")</f>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <f aca="false">COUNTIF(E21:P21,"A")</f>
         <v>0</v>
       </c>
-      <c r="T21" s="2" t="n">
-        <f aca="false">SUM(R21:S21)</f>
-        <v>9</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <f aca="false">ROUND(R21*10/T21,0)</f>
-        <v>10</v>
-      </c>
-      <c r="V21" s="4" t="str">
-        <f aca="false">IF(U21&gt;6,"TEA",IF(U21&gt;3,"TEP","TED"))</f>
+      <c r="S21" s="3" t="n">
+        <f aca="false">SUM(Q21:R21)</f>
+        <v>9</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <f aca="false">ROUND(Q21*10/S21,0)</f>
+        <v>10</v>
+      </c>
+      <c r="U21" s="1" t="str">
+        <f aca="false">IF(T21&gt;6,"TEA",IF(T21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="W21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z21" s="1" t="n">
+      <c r="V21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AB21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC21" s="1" t="n">
+      <c r="AA21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB21" s="1" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="AD21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE21" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AH21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="XCZ21" s="0"/>
+    </row>
+    <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="XCZ22" s="0"/>
+    </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <f aca="false">COUNTIF(E2:E22,"P")</f>
+        <v>18</v>
       </c>
       <c r="F23" s="1" t="n">
         <f aca="false">COUNTIF(F2:F22,"P")</f>
@@ -3044,19 +3416,19 @@
       </c>
       <c r="G23" s="1" t="n">
         <f aca="false">COUNTIF(G2:G22,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <f aca="false">COUNTIF(I2:I22,"P")</f>
         <v>18</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <f aca="false">COUNTIF(H2:H22,"P")</f>
+      <c r="K23" s="1" t="n">
+        <f aca="false">COUNTIF(K2:K22,"P")</f>
         <v>19</v>
       </c>
-      <c r="J23" s="1" t="n">
-        <f aca="false">COUNTIF(J2:J22,"P")</f>
-        <v>18</v>
-      </c>
-      <c r="L23" s="1" t="n">
-        <f aca="false">COUNTIF(L2:L22,"P")</f>
-        <v>19</v>
+      <c r="M23" s="1" t="n">
+        <f aca="false">COUNTIF(M2:M22,"P")</f>
+        <v>20</v>
       </c>
       <c r="N23" s="1" t="n">
         <f aca="false">COUNTIF(N2:N22,"P")</f>
@@ -3064,37 +3436,45 @@
       </c>
       <c r="O23" s="1" t="n">
         <f aca="false">COUNTIF(O2:O22,"P")</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P23" s="1" t="n">
         <f aca="false">COUNTIF(P2:P22,"P")</f>
         <v>19</v>
       </c>
-      <c r="Q23" s="1" t="n">
-        <f aca="false">COUNTIF(Q2:Q22,"P")</f>
+      <c r="V23" s="1" t="n">
+        <f aca="false">COUNTIF(V2:V22,"P")</f>
+        <v>18</v>
+      </c>
+      <c r="X23" s="1" t="n">
+        <f aca="false">COUNTIF(X2:X22,"P")</f>
         <v>19</v>
       </c>
-      <c r="W23" s="1" t="n">
-        <f aca="false">COUNTIF(W2:W22,"P")</f>
+      <c r="AA23" s="1" t="n">
+        <f aca="false">COUNTIF(AA2:AA22,"P")</f>
         <v>18</v>
       </c>
-      <c r="Y23" s="1" t="n">
-        <f aca="false">COUNTIF(Y2:Y22,"P")</f>
-        <v>19</v>
-      </c>
-      <c r="AB23" s="1" t="n">
-        <f aca="false">COUNTIF(AB2:AB22,"P")</f>
-        <v>18</v>
-      </c>
-      <c r="AC23" s="1"/>
-      <c r="AD23" s="1"/>
+      <c r="AD23" s="1" t="n">
+        <f aca="false">COUNTIF(AD2:AD22,"P")</f>
+        <v>20</v>
+      </c>
+      <c r="AE23" s="1"/>
+      <c r="AG23" s="1" t="n">
+        <f aca="false">COUNTIF(AG2:AG22,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="AH23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E17,"M")</f>
+        <v>0</v>
       </c>
       <c r="F24" s="1" t="n">
         <f aca="false">COUNTIF(F3:F17,"M")</f>
@@ -3104,16 +3484,16 @@
         <f aca="false">COUNTIF(G3:G17,"M")</f>
         <v>0</v>
       </c>
-      <c r="H24" s="1" t="n">
-        <f aca="false">COUNTIF(H3:H17,"M")</f>
+      <c r="I24" s="1" t="n">
+        <f aca="false">COUNTIF(I3:I17,"M")</f>
         <v>0</v>
       </c>
-      <c r="J24" s="1" t="n">
-        <f aca="false">COUNTIF(J3:J17,"M")</f>
+      <c r="K24" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K17,"M")</f>
         <v>0</v>
       </c>
-      <c r="L24" s="1" t="n">
-        <f aca="false">COUNTIF(L3:L17,"M")</f>
+      <c r="M24" s="1" t="n">
+        <f aca="false">COUNTIF(M3:M17,"M")</f>
         <v>0</v>
       </c>
       <c r="N24" s="1" t="n">
@@ -3128,31 +3508,39 @@
         <f aca="false">COUNTIF(P3:P17,"M")</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="1" t="n">
-        <f aca="false">COUNTIF(Q3:Q17,"M")</f>
+      <c r="V24" s="1" t="n">
+        <f aca="false">COUNTIF(V3:V17,"M")</f>
         <v>0</v>
       </c>
-      <c r="W24" s="1" t="n">
-        <f aca="false">COUNTIF(W3:W17,"M")</f>
+      <c r="X24" s="1" t="n">
+        <f aca="false">COUNTIF(X3:X17,"M")</f>
         <v>0</v>
       </c>
-      <c r="Y24" s="1" t="n">
-        <f aca="false">COUNTIF(Y3:Y17,"M")</f>
+      <c r="AA24" s="1" t="n">
+        <f aca="false">COUNTIF(AA3:AA17,"M")</f>
         <v>0</v>
       </c>
-      <c r="AB24" s="1" t="n">
-        <f aca="false">COUNTIF(AB3:AB17,"M")</f>
+      <c r="AD24" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD17,"M")</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AG24" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG17,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AH24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E17,"T")</f>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="n">
         <f aca="false">COUNTIF(F3:F17,"T")</f>
@@ -3162,16 +3550,16 @@
         <f aca="false">COUNTIF(G3:G17,"T")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="1" t="n">
-        <f aca="false">COUNTIF(H3:H17,"T")</f>
+      <c r="I25" s="1" t="n">
+        <f aca="false">COUNTIF(I3:I17,"T")</f>
         <v>0</v>
       </c>
-      <c r="J25" s="1" t="n">
-        <f aca="false">COUNTIF(J3:J17,"T")</f>
+      <c r="K25" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K17,"T")</f>
         <v>0</v>
       </c>
-      <c r="L25" s="1" t="n">
-        <f aca="false">COUNTIF(L3:L17,"T")</f>
+      <c r="M25" s="1" t="n">
+        <f aca="false">COUNTIF(M3:M17,"T")</f>
         <v>0</v>
       </c>
       <c r="N25" s="1" t="n">
@@ -3186,28 +3574,36 @@
         <f aca="false">COUNTIF(P3:P17,"T")</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="1" t="n">
-        <f aca="false">COUNTIF(Q3:Q17,"T")</f>
+      <c r="V25" s="1" t="n">
+        <f aca="false">COUNTIF(V3:V17,"T")</f>
         <v>0</v>
       </c>
-      <c r="W25" s="1" t="n">
-        <f aca="false">COUNTIF(W3:W17,"T")</f>
+      <c r="X25" s="1" t="n">
+        <f aca="false">COUNTIF(X3:X17,"T")</f>
         <v>0</v>
       </c>
-      <c r="Y25" s="1" t="n">
-        <f aca="false">COUNTIF(Y3:Y17,"T")</f>
+      <c r="AA25" s="1" t="n">
+        <f aca="false">COUNTIF(AA3:AA17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AB25" s="1" t="n">
-        <f aca="false">COUNTIF(AB3:AB17,"T")</f>
+      <c r="AD25" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AG25" s="1" t="n">
+        <f aca="false">COUNTIF(AG3:AG17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AH25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <f aca="false">SUM(E23:E25)</f>
+        <v>18</v>
       </c>
       <c r="F26" s="1" t="n">
         <f aca="false">SUM(F23:F25)</f>
@@ -3215,19 +3611,19 @@
       </c>
       <c r="G26" s="1" t="n">
         <f aca="false">SUM(G23:G25)</f>
+        <v>19</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <f aca="false">SUM(I23:I25)</f>
         <v>18</v>
       </c>
-      <c r="H26" s="1" t="n">
-        <f aca="false">SUM(H23:H25)</f>
+      <c r="K26" s="1" t="n">
+        <f aca="false">SUM(K23:K25)</f>
         <v>19</v>
       </c>
-      <c r="J26" s="1" t="n">
-        <f aca="false">SUM(J23:J25)</f>
-        <v>18</v>
-      </c>
-      <c r="L26" s="1" t="n">
-        <f aca="false">SUM(L23:L25)</f>
-        <v>19</v>
+      <c r="M26" s="1" t="n">
+        <f aca="false">SUM(M23:M25)</f>
+        <v>20</v>
       </c>
       <c r="N26" s="1" t="n">
         <f aca="false">SUM(N23:N25)</f>
@@ -3235,62 +3631,66 @@
       </c>
       <c r="O26" s="1" t="n">
         <f aca="false">SUM(O23:O25)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P26" s="1" t="n">
         <f aca="false">SUM(P23:P25)</f>
         <v>19</v>
       </c>
-      <c r="Q26" s="1" t="n">
-        <f aca="false">SUM(Q23:Q25)</f>
+      <c r="V26" s="1" t="n">
+        <f aca="false">SUM(V23:V25)</f>
+        <v>18</v>
+      </c>
+      <c r="X26" s="1" t="n">
+        <f aca="false">SUM(X23:X25)</f>
         <v>19</v>
       </c>
-      <c r="W26" s="1" t="n">
-        <f aca="false">SUM(W23:W25)</f>
+      <c r="AA26" s="1" t="n">
+        <f aca="false">SUM(AA23:AA25)</f>
         <v>18</v>
       </c>
-      <c r="Y26" s="1" t="n">
-        <f aca="false">SUM(Y23:Y25)</f>
-        <v>19</v>
-      </c>
-      <c r="AB26" s="1" t="n">
-        <f aca="false">SUM(AB23:AB25)</f>
-        <v>18</v>
-      </c>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
+      <c r="AD26" s="1" t="n">
+        <f aca="false">SUM(AD23:AD25)</f>
+        <v>20</v>
+      </c>
+      <c r="AE26" s="1"/>
+      <c r="AG26" s="1" t="n">
+        <f aca="false">SUM(AG23:AG25)</f>
+        <v>14</v>
+      </c>
+      <c r="AH26" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="U2:U21">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="T2:T21">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V21">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+  <conditionalFormatting sqref="U2:U21">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="6" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3324,7 +3724,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="2"/>
+      <c r="B1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -3340,22 +3740,22 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3363,13 +3763,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>10</v>
@@ -3396,13 +3796,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>7</v>
@@ -3429,13 +3829,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>1</v>
@@ -3462,13 +3862,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1</v>
@@ -3495,13 +3895,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>9</v>
@@ -3528,13 +3928,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>10</v>
@@ -3561,13 +3961,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>1</v>
@@ -3594,13 +3994,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>8</v>
@@ -3627,13 +4027,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>10</v>
@@ -3660,13 +4060,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>9</v>
@@ -3690,13 +4090,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>9</v>
@@ -3720,13 +4120,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>9</v>
@@ -3750,13 +4150,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>8</v>
@@ -3780,13 +4180,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>8</v>
@@ -3810,13 +4210,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>8</v>
@@ -3840,13 +4240,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>8</v>
@@ -3870,13 +4270,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>9</v>
@@ -3900,13 +4300,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>9</v>
@@ -3930,13 +4330,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>9</v>
@@ -3960,13 +4360,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>9</v>
@@ -3987,26 +4387,26 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F3:J22">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/inasistencias-4b-ElectYsistDeComTP/alumnos-4b-ElectroYSistDeCom.xlsx
+++ b/inasistencias-4b-ElectYsistDeComTP/alumnos-4b-ElectroYSistDeCom.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="93">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -77,6 +77,9 @@
     <t xml:space="preserve">arreglar el ladron de joules, soldar el capacitor, colocar todo en cajita y probar en clase la parte</t>
   </si>
   <si>
+    <t xml:space="preserve">emprolijar la cajita</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eugenia</t>
   </si>
   <si>
@@ -137,6 +140,9 @@
     <t xml:space="preserve">soldar los componentes , todo unto en una cajita. llevar el modelo al video, si funciona mantenemos el 10</t>
   </si>
   <si>
+    <t xml:space="preserve">ttradr un video donde se me mida con un tester la generacion de energia, ver de hacer un ladron de joules y un diodo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Julieta</t>
   </si>
   <si>
@@ -173,6 +179,9 @@
     <t xml:space="preserve">trajeron panel, controlaor, bateria, cables</t>
   </si>
   <si>
+    <t xml:space="preserve">armar un video con la generacion y la carga de la bateria</t>
+  </si>
+  <si>
     <t xml:space="preserve">Farid Emir</t>
   </si>
   <si>
@@ -207,6 +216,12 @@
   </si>
   <si>
     <t xml:space="preserve">armar un ladron de joules y por lo menos 3 tapers conectados en serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no trajo nada </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> no trajo nada</t>
   </si>
   <si>
     <t xml:space="preserve">Paloma Marianella</t>
@@ -296,7 +311,7 @@
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -317,12 +332,6 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="0"/>
     </font>
   </fonts>
@@ -374,7 +383,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -395,10 +404,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -407,12 +412,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -424,46 +425,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFFCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF006600"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -742,20 +704,20 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="31.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.62"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="6" style="1" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.32"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="13" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.62"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="11" min="6" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="1" width="13.32"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="13" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="63.84"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="25" min="24" style="1" width="8.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="53.33"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="27" style="1" width="8.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="63.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="60.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="81.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16327" min="16327" style="1" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16328" min="16328" style="0" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16329" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="81.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="37" style="1" width="18.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16328" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -864,73 +826,76 @@
         <v>46227</v>
       </c>
       <c r="AK1" s="2" t="n">
-        <v>46234</v>
-      </c>
-      <c r="AL1" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM1" s="2" t="n">
         <v>46241</v>
       </c>
-      <c r="AM1" s="2" t="n">
+      <c r="AN1" s="2" t="n">
         <v>46248</v>
       </c>
-      <c r="AN1" s="2" t="n">
+      <c r="AO1" s="2" t="n">
         <v>46255</v>
       </c>
-      <c r="AO1" s="2" t="n">
+      <c r="AP1" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="AP1" s="2" t="n">
+      <c r="AQ1" s="2" t="n">
         <v>46269</v>
       </c>
-      <c r="AQ1" s="2" t="n">
+      <c r="AR1" s="2" t="n">
         <v>46276</v>
       </c>
-      <c r="AR1" s="2" t="n">
+      <c r="AS1" s="2" t="n">
         <v>46283</v>
       </c>
-      <c r="AS1" s="2" t="n">
+      <c r="AT1" s="2" t="n">
         <v>46290</v>
       </c>
-      <c r="AT1" s="2" t="n">
+      <c r="AU1" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="AU1" s="2" t="n">
+      <c r="AV1" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="AV1" s="2" t="n">
+      <c r="AW1" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="AW1" s="2" t="n">
+      <c r="AX1" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="AX1" s="2" t="n">
+      <c r="AY1" s="2" t="n">
         <v>46325</v>
       </c>
-      <c r="AY1" s="2" t="n">
+      <c r="AZ1" s="2" t="n">
         <v>46332</v>
       </c>
-      <c r="AZ1" s="2" t="n">
+      <c r="BA1" s="2" t="n">
         <v>46339</v>
       </c>
-      <c r="BA1" s="2" t="n">
+      <c r="BB1" s="2" t="n">
         <v>46346</v>
       </c>
-      <c r="BB1" s="2" t="n">
+      <c r="BC1" s="2" t="n">
         <v>46353</v>
       </c>
-      <c r="BC1" s="2" t="n">
+      <c r="BD1" s="2" t="n">
         <v>46360</v>
       </c>
-      <c r="BD1" s="2" t="n">
+      <c r="BE1" s="2" t="n">
         <v>46367</v>
       </c>
-      <c r="BE1" s="2" t="n">
+      <c r="BF1" s="2" t="n">
         <v>46374</v>
       </c>
-      <c r="BF1" s="2" t="n">
+      <c r="BG1" s="2" t="n">
         <v>46381</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -988,7 +953,7 @@
         <f aca="false">ROUND(Q2*10/S2,0)</f>
         <v>10</v>
       </c>
-      <c r="U2" s="1" t="str">
+      <c r="U2" s="4" t="str">
         <f aca="false">IF(T2&gt;6,"TEA",IF(T2&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -1028,28 +993,34 @@
       <c r="AG2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AH2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI2" s="0" t="n">
+      <c r="AH2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI2" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AJ2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="BG2" s="2"/>
+      <c r="AK2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="BH2" s="2"/>
       <c r="BI2" s="2"/>
-    </row>
-    <row r="3" s="3" customFormat="true" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="BJ2" s="2"/>
+    </row>
+    <row r="3" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>12</v>
@@ -1058,7 +1029,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>13</v>
@@ -1097,12 +1068,12 @@
         <f aca="false">ROUND(Q3*10/S3,0)</f>
         <v>9</v>
       </c>
-      <c r="U3" s="1" t="str">
+      <c r="U3" s="4" t="str">
         <f aca="false">IF(T3&gt;6,"TEA",IF(T3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X3" s="3" t="s">
         <v>13</v>
@@ -1132,8 +1103,10 @@
       <c r="AI3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="XCY3" s="1"/>
-      <c r="XCZ3" s="0"/>
+      <c r="AK3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="XCZ3" s="1"/>
       <c r="XDA3" s="1"/>
       <c r="XDB3" s="1"/>
       <c r="XDC3" s="1"/>
@@ -1196,10 +1169,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
@@ -1247,7 +1220,7 @@
         <f aca="false">ROUND(Q4*10/S4,0)</f>
         <v>10</v>
       </c>
-      <c r="U4" s="1" t="str">
+      <c r="U4" s="4" t="str">
         <f aca="false">IF(T4&gt;6,"TEA",IF(T4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -1282,8 +1255,10 @@
       <c r="AI4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="XCY4" s="1"/>
-      <c r="XCZ4" s="0"/>
+      <c r="AK4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="XCZ4" s="1"/>
       <c r="XDA4" s="1"/>
       <c r="XDB4" s="1"/>
       <c r="XDC4" s="1"/>
@@ -1346,10 +1321,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
@@ -1397,7 +1372,7 @@
         <f aca="false">ROUND(Q5*10/S5,0)</f>
         <v>10</v>
       </c>
-      <c r="U5" s="1" t="str">
+      <c r="U5" s="4" t="str">
         <f aca="false">IF(T5&gt;6,"TEA",IF(T5&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -1423,7 +1398,7 @@
         <v>7</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH5" s="1" t="s">
         <v>13</v>
@@ -1431,64 +1406,66 @@
       <c r="AI5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="XCZ5" s="0"/>
+      <c r="AK5" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q6" s="6" t="n">
+      <c r="E6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q6" s="5" t="n">
         <f aca="false">COUNTIF(E6:P6,"P")</f>
         <v>7</v>
       </c>
-      <c r="R6" s="7" t="n">
+      <c r="R6" s="6" t="n">
         <f aca="false">COUNTIF(E6:P6,"A")</f>
         <v>2</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="S6" s="5" t="n">
         <f aca="false">SUM(Q6:R6)</f>
         <v>9</v>
       </c>
@@ -1496,11 +1473,11 @@
         <f aca="false">ROUND(Q6*10/S6,0)</f>
         <v>8</v>
       </c>
-      <c r="U6" s="1" t="str">
+      <c r="U6" s="4" t="str">
         <f aca="false">IF(T6&gt;6,"TEA",IF(T6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="V6" s="7" t="s">
+      <c r="V6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="X6" s="1" t="s">
@@ -1521,26 +1498,28 @@
       <c r="AE6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH6" s="7" t="s">
+      <c r="AG6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="AI6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="XCZ6" s="0"/>
+      <c r="AK6" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>12</v>
@@ -1588,7 +1567,7 @@
         <f aca="false">ROUND(Q7*10/S7,0)</f>
         <v>10</v>
       </c>
-      <c r="U7" s="1" t="str">
+      <c r="U7" s="4" t="str">
         <f aca="false">IF(T7&gt;6,"TEA",IF(T7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -1622,20 +1601,22 @@
       <c r="AI7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="XCZ7" s="0"/>
+      <c r="AK7" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" s="3" customFormat="true" ht="33.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>13</v>
@@ -1650,10 +1631,10 @@
         <v>13</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>13</v>
@@ -1683,7 +1664,7 @@
         <f aca="false">ROUND(Q8*10/S8,0)</f>
         <v>9</v>
       </c>
-      <c r="U8" s="1" t="str">
+      <c r="U8" s="4" t="str">
         <f aca="false">IF(T8&gt;6,"TEA",IF(T8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -1691,7 +1672,7 @@
         <v>13</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="X8" s="3" t="s">
         <v>13</v>
@@ -1700,7 +1681,7 @@
         <v>3</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>13</v>
@@ -1715,7 +1696,7 @@
         <v>3</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG8" s="1" t="s">
         <v>13</v>
@@ -1726,11 +1707,17 @@
       <c r="AI8" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AJ8" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="XCY8" s="1"/>
-      <c r="XCZ8" s="0"/>
+      <c r="AJ8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM8" s="7"/>
+      <c r="XCZ8" s="1"/>
       <c r="XDA8" s="1"/>
       <c r="XDB8" s="1"/>
       <c r="XDC8" s="1"/>
@@ -1793,13 +1780,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>13</v>
@@ -1825,7 +1812,7 @@
         <v>13</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>13</v>
@@ -1846,7 +1833,7 @@
         <f aca="false">ROUND(Q9*10/S9,0)</f>
         <v>10</v>
       </c>
-      <c r="U9" s="1" t="str">
+      <c r="U9" s="4" t="str">
         <f aca="false">IF(T9&gt;6,"TEA",IF(T9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -1867,7 +1854,7 @@
         <v>7</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AD9" s="3" t="s">
         <v>13</v>
@@ -1885,8 +1872,10 @@
       <c r="AI9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="XCY9" s="1"/>
-      <c r="XCZ9" s="0"/>
+      <c r="AK9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="XCZ9" s="1"/>
       <c r="XDA9" s="1"/>
       <c r="XDB9" s="1"/>
       <c r="XDC9" s="1"/>
@@ -1949,13 +1938,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>13</v>
@@ -1967,7 +1956,7 @@
         <v>13</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>13</v>
@@ -2001,7 +1990,7 @@
         <f aca="false">ROUND(Q10*10/S10,0)</f>
         <v>9</v>
       </c>
-      <c r="U10" s="1" t="str">
+      <c r="U10" s="4" t="str">
         <f aca="false">IF(T10&gt;6,"TEA",IF(T10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -2036,8 +2025,10 @@
       <c r="AI10" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="XCY10" s="1"/>
-      <c r="XCZ10" s="0"/>
+      <c r="AK10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="XCZ10" s="1"/>
       <c r="XDA10" s="1"/>
       <c r="XDB10" s="1"/>
       <c r="XDC10" s="1"/>
@@ -2095,18 +2086,18 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" s="1" customFormat="true" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>13</v>
@@ -2133,7 +2124,7 @@
         <v>13</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q11" s="3" t="n">
         <f aca="false">COUNTIF(E11:P11,"P")</f>
@@ -2151,7 +2142,7 @@
         <f aca="false">ROUND(Q11*10/S11,0)</f>
         <v>9</v>
       </c>
-      <c r="U11" s="1" t="str">
+      <c r="U11" s="4" t="str">
         <f aca="false">IF(T11&gt;6,"TEA",IF(T11&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -2159,7 +2150,7 @@
         <v>13</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="X11" s="1" t="s">
         <v>13</v>
@@ -2168,7 +2159,7 @@
         <v>5</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AA11" s="1" t="s">
         <v>13</v>
@@ -2183,7 +2174,7 @@
         <v>9</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AG11" s="1" t="s">
         <v>13</v>
@@ -2195,22 +2186,27 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="XCZ11" s="0"/>
-    </row>
-    <row r="12" s="1" customFormat="true" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL11" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
@@ -2256,7 +2252,7 @@
         <f aca="false">ROUND(Q12*10/S12,0)</f>
         <v>10</v>
       </c>
-      <c r="U12" s="1" t="str">
+      <c r="U12" s="4" t="str">
         <f aca="false">IF(T12&gt;6,"TEA",IF(T12&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -2270,7 +2266,7 @@
         <v>1</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB12" s="1" t="n">
         <v>3</v>
@@ -2282,7 +2278,7 @@
         <v>9</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>13</v>
@@ -2294,22 +2290,24 @@
         <v>1</v>
       </c>
       <c r="AJ12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="XCZ12" s="0"/>
+        <v>55</v>
+      </c>
+      <c r="AK12" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>13</v>
@@ -2356,12 +2354,12 @@
         <f aca="false">ROUND(Q13*10/S13,0)</f>
         <v>10</v>
       </c>
-      <c r="U13" s="1" t="str">
+      <c r="U13" s="4" t="str">
         <f aca="false">IF(T13&gt;6,"TEA",IF(T13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="X13" s="1" t="s">
         <v>13</v>
@@ -2382,31 +2380,33 @@
         <v>9</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI13" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="XCZ13" s="0"/>
+      <c r="AK13" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="14" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>13</v>
@@ -2428,7 +2428,7 @@
         <v>13</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>13</v>
@@ -2449,7 +2449,7 @@
         <f aca="false">ROUND(Q14*10/S14,0)</f>
         <v>8</v>
       </c>
-      <c r="U14" s="1" t="str">
+      <c r="U14" s="4" t="str">
         <f aca="false">IF(T14&gt;6,"TEA",IF(T14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>13</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>13</v>
@@ -2466,16 +2466,16 @@
         <v>7</v>
       </c>
       <c r="Z14" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB14" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>13</v>
@@ -2484,10 +2484,10 @@
         <v>10</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH14" s="1" t="s">
         <v>13</v>
@@ -2495,77 +2495,85 @@
       <c r="AI14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="XCY14" s="1"/>
-      <c r="XCZ14" s="0"/>
-      <c r="XDA14" s="6"/>
-      <c r="XDB14" s="6"/>
-      <c r="XDC14" s="6"/>
-      <c r="XDD14" s="6"/>
-      <c r="XDE14" s="6"/>
-      <c r="XDF14" s="6"/>
-      <c r="XDG14" s="6"/>
-      <c r="XDH14" s="6"/>
-      <c r="XDI14" s="6"/>
-      <c r="XDJ14" s="6"/>
-      <c r="XDK14" s="6"/>
-      <c r="XDL14" s="6"/>
-      <c r="XDM14" s="6"/>
-      <c r="XDN14" s="6"/>
-      <c r="XDO14" s="6"/>
-      <c r="XDP14" s="6"/>
-      <c r="XDQ14" s="6"/>
-      <c r="XDR14" s="6"/>
-      <c r="XDS14" s="6"/>
-      <c r="XDT14" s="6"/>
-      <c r="XDU14" s="6"/>
-      <c r="XDV14" s="6"/>
-      <c r="XDW14" s="6"/>
-      <c r="XDX14" s="6"/>
-      <c r="XDY14" s="6"/>
-      <c r="XDZ14" s="6"/>
-      <c r="XEA14" s="6"/>
-      <c r="XEB14" s="6"/>
-      <c r="XEC14" s="6"/>
-      <c r="XED14" s="6"/>
-      <c r="XEE14" s="6"/>
-      <c r="XEF14" s="6"/>
-      <c r="XEG14" s="6"/>
-      <c r="XEH14" s="6"/>
-      <c r="XEI14" s="6"/>
-      <c r="XEJ14" s="6"/>
-      <c r="XEK14" s="6"/>
-      <c r="XEL14" s="6"/>
-      <c r="XEM14" s="6"/>
-      <c r="XEN14" s="6"/>
-      <c r="XEO14" s="6"/>
-      <c r="XEP14" s="6"/>
-      <c r="XEQ14" s="6"/>
-      <c r="XER14" s="6"/>
-      <c r="XES14" s="6"/>
-      <c r="XET14" s="6"/>
-      <c r="XEU14" s="6"/>
-      <c r="XEV14" s="6"/>
-      <c r="XEW14" s="6"/>
-      <c r="XEX14" s="6"/>
-      <c r="XEY14" s="6"/>
-      <c r="XEZ14" s="6"/>
-      <c r="XFA14" s="6"/>
-      <c r="XFB14" s="6"/>
-      <c r="XFC14" s="6"/>
-      <c r="XFD14" s="6"/>
-    </row>
-    <row r="15" s="7" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AJ14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="XCZ14" s="1"/>
+      <c r="XDA14" s="1"/>
+      <c r="XDB14" s="5"/>
+      <c r="XDC14" s="5"/>
+      <c r="XDD14" s="5"/>
+      <c r="XDE14" s="5"/>
+      <c r="XDF14" s="5"/>
+      <c r="XDG14" s="5"/>
+      <c r="XDH14" s="5"/>
+      <c r="XDI14" s="5"/>
+      <c r="XDJ14" s="5"/>
+      <c r="XDK14" s="5"/>
+      <c r="XDL14" s="5"/>
+      <c r="XDM14" s="5"/>
+      <c r="XDN14" s="5"/>
+      <c r="XDO14" s="5"/>
+      <c r="XDP14" s="5"/>
+      <c r="XDQ14" s="5"/>
+      <c r="XDR14" s="5"/>
+      <c r="XDS14" s="5"/>
+      <c r="XDT14" s="5"/>
+      <c r="XDU14" s="5"/>
+      <c r="XDV14" s="5"/>
+      <c r="XDW14" s="5"/>
+      <c r="XDX14" s="5"/>
+      <c r="XDY14" s="5"/>
+      <c r="XDZ14" s="5"/>
+      <c r="XEA14" s="5"/>
+      <c r="XEB14" s="5"/>
+      <c r="XEC14" s="5"/>
+      <c r="XED14" s="5"/>
+      <c r="XEE14" s="5"/>
+      <c r="XEF14" s="5"/>
+      <c r="XEG14" s="5"/>
+      <c r="XEH14" s="5"/>
+      <c r="XEI14" s="5"/>
+      <c r="XEJ14" s="5"/>
+      <c r="XEK14" s="5"/>
+      <c r="XEL14" s="5"/>
+      <c r="XEM14" s="5"/>
+      <c r="XEN14" s="5"/>
+      <c r="XEO14" s="5"/>
+      <c r="XEP14" s="5"/>
+      <c r="XEQ14" s="5"/>
+      <c r="XER14" s="5"/>
+      <c r="XES14" s="5"/>
+      <c r="XET14" s="5"/>
+      <c r="XEU14" s="5"/>
+      <c r="XEV14" s="5"/>
+      <c r="XEW14" s="5"/>
+      <c r="XEX14" s="5"/>
+      <c r="XEY14" s="5"/>
+      <c r="XEZ14" s="5"/>
+      <c r="XFA14" s="5"/>
+      <c r="XFB14" s="5"/>
+      <c r="XFC14" s="5"/>
+      <c r="XFD14" s="5"/>
+    </row>
+    <row r="15" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>13</v>
@@ -2613,23 +2621,23 @@
         <f aca="false">ROUND(Q15*10/S15,0)</f>
         <v>10</v>
       </c>
-      <c r="U15" s="1" t="str">
+      <c r="U15" s="4" t="str">
         <f aca="false">IF(T15&gt;6,"TEA",IF(T15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="X15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y15" s="7" t="n">
+      <c r="X15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y15" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="AA15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB15" s="7" t="n">
+      <c r="AA15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB15" s="6" t="n">
         <v>5</v>
       </c>
       <c r="AD15" s="3" t="s">
@@ -2645,11 +2653,13 @@
       <c r="AH15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AI15" s="7" t="n">
+      <c r="AI15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="XCY15" s="1"/>
-      <c r="XCZ15" s="0"/>
+      <c r="AK15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="XCZ15" s="1"/>
       <c r="XDA15" s="1"/>
       <c r="XDB15" s="1"/>
       <c r="XDC15" s="1"/>
@@ -2712,13 +2722,13 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>13</v>
@@ -2727,7 +2737,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>13</v>
@@ -2763,7 +2773,7 @@
         <f aca="false">ROUND(Q16*10/S16,0)</f>
         <v>9</v>
       </c>
-      <c r="U16" s="1" t="str">
+      <c r="U16" s="4" t="str">
         <f aca="false">IF(T16&gt;6,"TEA",IF(T16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -2772,7 +2782,7 @@
       </c>
       <c r="W16" s="1"/>
       <c r="X16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>7</v>
@@ -2791,7 +2801,7 @@
       </c>
       <c r="AF16" s="1"/>
       <c r="AG16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH16" s="3" t="s">
         <v>13</v>
@@ -2799,8 +2809,10 @@
       <c r="AI16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="XCY16" s="1"/>
-      <c r="XCZ16" s="0"/>
+      <c r="AK16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="XCZ16" s="1"/>
       <c r="XDA16" s="1"/>
       <c r="XDB16" s="1"/>
       <c r="XDC16" s="1"/>
@@ -2863,13 +2875,13 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>13</v>
@@ -2915,7 +2927,7 @@
         <f aca="false">ROUND(Q17*10/S17,0)</f>
         <v>10</v>
       </c>
-      <c r="U17" s="1" t="str">
+      <c r="U17" s="4" t="str">
         <f aca="false">IF(T17&gt;6,"TEA",IF(T17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -2942,7 +2954,7 @@
       </c>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH17" s="1" t="s">
         <v>13</v>
@@ -2950,8 +2962,10 @@
       <c r="AI17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="XCY17" s="1"/>
-      <c r="XCZ17" s="0"/>
+      <c r="AK17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="XCZ17" s="1"/>
       <c r="XDA17" s="1"/>
       <c r="XDB17" s="1"/>
       <c r="XDC17" s="1"/>
@@ -3009,18 +3023,18 @@
       <c r="XFC17" s="1"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" s="1" customFormat="true" ht="16.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>13</v>
@@ -3045,7 +3059,7 @@
         <v>13</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>13</v>
@@ -3066,7 +3080,7 @@
         <f aca="false">ROUND(Q18*10/S18,0)</f>
         <v>10</v>
       </c>
-      <c r="U18" s="1" t="str">
+      <c r="U18" s="4" t="str">
         <f aca="false">IF(T18&gt;6,"TEA",IF(T18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -3074,7 +3088,7 @@
         <v>13</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="X18" s="1" t="s">
         <v>13</v>
@@ -3083,7 +3097,7 @@
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AA18" s="1" t="s">
         <v>13</v>
@@ -3092,7 +3106,7 @@
         <v>7</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AD18" s="3" t="s">
         <v>13</v>
@@ -3100,8 +3114,8 @@
       <c r="AE18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AF18" s="9" t="s">
-        <v>71</v>
+      <c r="AF18" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>13</v>
@@ -3112,23 +3126,28 @@
       <c r="AI18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AJ18" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="XCZ18" s="0"/>
+      <c r="AJ18" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL18" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="19" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>13</v>
@@ -3141,7 +3160,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
@@ -3176,7 +3195,7 @@
         <f aca="false">ROUND(Q19*10/S19,0)</f>
         <v>9</v>
       </c>
-      <c r="U19" s="1" t="str">
+      <c r="U19" s="4" t="str">
         <f aca="false">IF(T19&gt;6,"TEA",IF(T19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -3210,21 +3229,23 @@
       <c r="AI19" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="XCZ19" s="0"/>
+      <c r="AK19" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="E20" s="1" t="s">
         <v>13</v>
       </c>
@@ -3250,7 +3271,7 @@
         <v>13</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q20" s="3" t="n">
         <f aca="false">COUNTIF(E20:P20,"P")</f>
@@ -3268,7 +3289,7 @@
         <f aca="false">ROUND(Q20*10/S20,0)</f>
         <v>10</v>
       </c>
-      <c r="U20" s="1" t="str">
+      <c r="U20" s="4" t="str">
         <f aca="false">IF(T20&gt;6,"TEA",IF(T20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -3302,20 +3323,22 @@
       <c r="AI20" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="XCZ20" s="0"/>
+      <c r="AK20" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>13</v>
@@ -3360,7 +3383,7 @@
         <f aca="false">ROUND(Q21*10/S21,0)</f>
         <v>10</v>
       </c>
-      <c r="U21" s="1" t="str">
+      <c r="U21" s="4" t="str">
         <f aca="false">IF(T21&gt;6,"TEA",IF(T21&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -3386,22 +3409,22 @@
         <v>7</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="XCZ21" s="0"/>
-    </row>
-    <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XCZ22" s="0"/>
-    </row>
+      <c r="AK21" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>5</v>
@@ -3464,13 +3487,17 @@
         <v>14</v>
       </c>
       <c r="AH23" s="1"/>
+      <c r="AK23" s="1" t="n">
+        <f aca="false">COUNTIF(AK2:AK22,"P")</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E24" s="1" t="n">
         <f aca="false">COUNTIF(E3:E17,"M")</f>
@@ -3530,13 +3557,17 @@
         <v>0</v>
       </c>
       <c r="AH24" s="1"/>
+      <c r="AK24" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK17,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E25" s="1" t="n">
         <f aca="false">COUNTIF(E3:E17,"T")</f>
@@ -3596,6 +3627,10 @@
         <v>0</v>
       </c>
       <c r="AH25" s="1"/>
+      <c r="AK25" s="1" t="n">
+        <f aca="false">COUNTIF(AK3:AK17,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
@@ -3659,38 +3694,42 @@
         <v>14</v>
       </c>
       <c r="AH26" s="1"/>
+      <c r="AK26" s="1" t="n">
+        <f aca="false">SUM(AK23:AK25)</f>
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="T2:T21">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U21">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="6" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="7" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3740,22 +3779,22 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3796,10 +3835,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>12</v>
@@ -3829,10 +3868,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>12</v>
@@ -3862,13 +3901,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1</v>
@@ -3895,13 +3934,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>9</v>
@@ -3928,13 +3967,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>10</v>
@@ -3961,13 +4000,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>1</v>
@@ -3994,13 +4033,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>8</v>
@@ -4027,13 +4066,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>10</v>
@@ -4060,13 +4099,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>9</v>
@@ -4090,10 +4129,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
@@ -4120,13 +4159,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>9</v>
@@ -4150,13 +4189,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>8</v>
@@ -4180,10 +4219,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>12</v>
@@ -4210,13 +4249,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>8</v>
@@ -4240,13 +4279,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>8</v>
@@ -4270,13 +4309,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>9</v>
@@ -4300,13 +4339,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>9</v>
@@ -4330,10 +4369,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>12</v>
@@ -4360,13 +4399,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>9</v>
@@ -4387,26 +4426,26 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F3:J22">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/inasistencias-4b-ElectYsistDeComTP/alumnos-4b-ElectroYSistDeCom.xlsx
+++ b/inasistencias-4b-ElectYsistDeComTP/alumnos-4b-ElectroYSistDeCom.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="104">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -53,6 +53,18 @@
     <t xml:space="preserve">Val Ped</t>
   </si>
   <si>
+    <t xml:space="preserve">Nota-EC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nota proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proy</t>
+  </si>
+  <si>
     <t xml:space="preserve">Victoria</t>
   </si>
   <si>
@@ -80,6 +92,12 @@
     <t xml:space="preserve">emprolijar la cajita</t>
   </si>
   <si>
+    <t xml:space="preserve">traer cajita, traer ladron de joules, video con todo andando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probarlo a full</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eugenia</t>
   </si>
   <si>
@@ -140,7 +158,10 @@
     <t xml:space="preserve">soldar los componentes , todo unto en una cajita. llevar el modelo al video, si funciona mantenemos el 10</t>
   </si>
   <si>
-    <t xml:space="preserve">ttradr un video donde se me mida con un tester la generacion de energia, ver de hacer un ladron de joules y un diodo</t>
+    <t xml:space="preserve">traer un video donde se me mida con un tester la generacion de energia, ver de hacer un ladron de joules y un diodo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">armar la otra mitad del ladron y generar la tension prometida  y grabar video</t>
   </si>
   <si>
     <t xml:space="preserve">Julieta</t>
@@ -182,6 +203,9 @@
     <t xml:space="preserve">armar un video con la generacion y la carga de la bateria</t>
   </si>
   <si>
+    <t xml:space="preserve">falta la carga de la bateria, agregar al video</t>
+  </si>
+  <si>
     <t xml:space="preserve">Farid Emir</t>
   </si>
   <si>
@@ -224,12 +248,18 @@
     <t xml:space="preserve"> no trajo nada</t>
   </si>
   <si>
+    <t xml:space="preserve">probar liquidos, mejorar prototipo y ladron de joules, conectar led, le di toroide</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paloma Marianella</t>
   </si>
   <si>
     <t xml:space="preserve">FARIAS RUIZ</t>
   </si>
   <si>
+    <t xml:space="preserve">subir un prototipo </t>
+  </si>
+  <si>
     <t xml:space="preserve">León</t>
   </si>
   <si>
@@ -255,6 +285,9 @@
   </si>
   <si>
     <t xml:space="preserve">no tenemos material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">probar baldoza con ladron de joules</t>
   </si>
   <si>
     <t xml:space="preserve">Thiago Ezquiel</t>
@@ -383,7 +416,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -401,6 +434,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -707,17 +744,24 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.62"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="11" min="6" style="1" width="8.79"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="1" width="13.32"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="21" min="13" style="1" width="8.79"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="63.84"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="25" min="24" style="1" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="53.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="28" min="27" style="1" width="8.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="63.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="60.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="81.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="37" style="1" width="18.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16328" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="22" min="13" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="23" min="23" style="1" width="63.84"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="25" min="24" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="1" width="53.33"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="28" min="27" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="29" min="29" style="1" width="63.84"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="31" min="30" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="32" style="1" width="60.08"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="35" min="33" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="36" min="36" style="1" width="81.26"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="37" min="37" style="1" width="18.33"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="38" min="38" style="1" width="63.23"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="40" min="39" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="41" min="41" style="1" width="63.23"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="43" min="42" style="1" width="8.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="65.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16334" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -832,66 +876,82 @@
         <v>4</v>
       </c>
       <c r="AM1" s="2" t="n">
-        <v>46241</v>
-      </c>
-      <c r="AN1" s="2" t="n">
-        <v>46248</v>
-      </c>
-      <c r="AO1" s="2" t="n">
-        <v>46255</v>
+        <v>46262</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="AP1" s="2" t="n">
-        <v>46262</v>
-      </c>
-      <c r="AQ1" s="2" t="n">
         <v>46269</v>
       </c>
-      <c r="AR1" s="2" t="n">
+      <c r="AQ1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS1" s="2" t="n">
         <v>46276</v>
       </c>
-      <c r="AS1" s="2" t="n">
+      <c r="AT1" s="2" t="n">
         <v>46283</v>
       </c>
-      <c r="AT1" s="2" t="n">
+      <c r="AU1" s="2" t="n">
         <v>46290</v>
       </c>
-      <c r="AU1" s="2" t="n">
+      <c r="AV1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX1" s="2"/>
+      <c r="AY1" s="2" t="n">
         <v>46297</v>
       </c>
-      <c r="AV1" s="2" t="n">
+      <c r="AZ1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="BB1" s="2" t="n">
         <v>46304</v>
       </c>
-      <c r="AW1" s="2" t="n">
+      <c r="BC1" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="AX1" s="2" t="n">
+      <c r="BD1" s="2" t="n">
         <v>46318</v>
       </c>
-      <c r="AY1" s="2" t="n">
+      <c r="BE1" s="2" t="n">
         <v>46325</v>
       </c>
-      <c r="AZ1" s="2" t="n">
+      <c r="BF1" s="2" t="n">
         <v>46332</v>
       </c>
-      <c r="BA1" s="2" t="n">
+      <c r="BG1" s="2" t="n">
         <v>46339</v>
       </c>
-      <c r="BB1" s="2" t="n">
+      <c r="BH1" s="2" t="n">
         <v>46346</v>
       </c>
-      <c r="BC1" s="2" t="n">
+      <c r="BI1" s="2" t="n">
         <v>46353</v>
       </c>
-      <c r="BD1" s="2" t="n">
+      <c r="BJ1" s="2" t="n">
         <v>46360</v>
       </c>
-      <c r="BE1" s="2" t="n">
+      <c r="BK1" s="2" t="n">
         <v>46367</v>
       </c>
-      <c r="BF1" s="2" t="n">
+      <c r="BL1" s="2" t="n">
         <v>46374</v>
       </c>
-      <c r="BG1" s="2" t="n">
+      <c r="BM1" s="2" t="n">
         <v>46381</v>
       </c>
     </row>
@@ -900,42 +960,42 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q2" s="3" t="n">
         <f aca="false">COUNTIF(E2:P2,"P")</f>
@@ -958,99 +1018,138 @@
         <v>TEA</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y2" s="1" t="n">
         <v>9</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB2" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE2" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI2" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AK2" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="BH2" s="2"/>
-      <c r="BI2" s="2"/>
-      <c r="BJ2" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="AM2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN2" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AT2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV2" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW2" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ2" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA2" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN2" s="2"/>
+      <c r="BO2" s="2"/>
+      <c r="BP2" s="2"/>
     </row>
     <row r="3" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q3" s="3" t="n">
         <f aca="false">COUNTIF(E3:P3,"P")</f>
@@ -1073,45 +1172,69 @@
         <v>TEA</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y3" s="3" t="n">
         <v>9</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB3" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AF3" s="1"/>
       <c r="AG3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XCZ3" s="1"/>
-      <c r="XDA3" s="1"/>
-      <c r="XDB3" s="1"/>
-      <c r="XDC3" s="1"/>
-      <c r="XDD3" s="1"/>
-      <c r="XDE3" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AT3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW3" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ3" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA3" s="0" t="n">
+        <v>6</v>
+      </c>
       <c r="XDF3" s="1"/>
       <c r="XDG3" s="1"/>
       <c r="XDH3" s="1"/>
@@ -1169,40 +1292,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="3" t="n">
         <f aca="false">COUNTIF(E4:P4,"P")</f>
@@ -1225,45 +1348,69 @@
         <v>TEA</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>9</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB4" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE4" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AF4" s="1"/>
       <c r="AG4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="XCZ4" s="1"/>
-      <c r="XDA4" s="1"/>
-      <c r="XDB4" s="1"/>
-      <c r="XDC4" s="1"/>
-      <c r="XDD4" s="1"/>
-      <c r="XDE4" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ4" s="1"/>
+      <c r="AR4" s="1"/>
+      <c r="AT4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW4" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX4" s="1"/>
+      <c r="AY4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ4" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA4" s="0" t="n">
+        <v>6</v>
+      </c>
       <c r="XDF4" s="1"/>
       <c r="XDG4" s="1"/>
       <c r="XDH4" s="1"/>
@@ -1316,45 +1463,45 @@
       <c r="XFC4" s="1"/>
       <c r="XFD4" s="1"/>
     </row>
-    <row r="5" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" s="1" customFormat="true" ht="18.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q5" s="3" t="n">
         <f aca="false">COUNTIF(E5:P5,"P")</f>
@@ -1377,95 +1524,122 @@
         <v>TEA</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y5" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB5" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE5" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AG5" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AH5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI5" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AK5" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY5" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ5" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA5" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="O6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q6" s="5" t="n">
+      <c r="F6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q6" s="6" t="n">
         <f aca="false">COUNTIF(E6:P6,"P")</f>
         <v>7</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="R6" s="7" t="n">
         <f aca="false">COUNTIF(E6:P6,"A")</f>
         <v>2</v>
       </c>
-      <c r="S6" s="5" t="n">
+      <c r="S6" s="6" t="n">
         <f aca="false">SUM(Q6:R6)</f>
         <v>9</v>
       </c>
@@ -1477,38 +1651,66 @@
         <f aca="false">IF(T6&gt;6,"TEA",IF(T6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="V6" s="6" t="s">
-        <v>13</v>
+      <c r="V6" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y6" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB6" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AD6" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE6" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH6" s="6" t="s">
-        <v>13</v>
+      <c r="AG6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH6" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AI6" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AK6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AM6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN6" s="7"/>
+      <c r="AP6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW6" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY6" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ6" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA6" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1516,40 +1718,40 @@
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q7" s="3" t="n">
         <f aca="false">COUNTIF(E7:P7,"P")</f>
@@ -1572,81 +1774,108 @@
         <v>TEA</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y7" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB7" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AD7" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI7" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ7" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA7" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="true" ht="33.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" s="3" customFormat="true" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q8" s="3" t="n">
         <f aca="false">COUNTIF(E8:P8,"P")</f>
@@ -1669,60 +1898,90 @@
         <v>TEA</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB8" s="3" t="n">
         <v>7</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE8" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AJ8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="AK8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="AM8" s="7"/>
-      <c r="XCZ8" s="1"/>
-      <c r="XDA8" s="1"/>
-      <c r="XDB8" s="1"/>
-      <c r="XDC8" s="1"/>
-      <c r="XDD8" s="1"/>
-      <c r="XDE8" s="1"/>
+      <c r="AJ8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX8" s="1"/>
+      <c r="AY8" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA8" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="XDF8" s="1"/>
       <c r="XDG8" s="1"/>
       <c r="XDH8" s="1"/>
@@ -1780,42 +2039,42 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q9" s="3" t="n">
         <f aca="false">COUNTIF(E9:P9,"P")</f>
@@ -1838,49 +2097,75 @@
         <v>TEA</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Z9" s="1"/>
       <c r="AA9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB9" s="3" t="n">
         <v>7</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE9" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AF9" s="1"/>
       <c r="AG9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="AK9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="XCZ9" s="1"/>
-      <c r="XDA9" s="1"/>
-      <c r="XDB9" s="1"/>
-      <c r="XDC9" s="1"/>
-      <c r="XDD9" s="1"/>
-      <c r="XDE9" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="AM9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR9" s="1"/>
+      <c r="AT9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX9" s="1"/>
+      <c r="AY9" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA9" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="XDF9" s="1"/>
       <c r="XDG9" s="1"/>
       <c r="XDH9" s="1"/>
@@ -1938,41 +2223,41 @@
         <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q10" s="3" t="n">
         <f aca="false">COUNTIF(E10:P10,"P")</f>
@@ -1995,45 +2280,72 @@
         <v>TEA</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>3</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB10" s="3" t="n">
         <v>7</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE10" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH10" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>10</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="XCZ10" s="1"/>
-      <c r="XDA10" s="1"/>
-      <c r="XDB10" s="1"/>
-      <c r="XDC10" s="1"/>
-      <c r="XDD10" s="1"/>
-      <c r="XDE10" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="AM10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN10" s="1"/>
+      <c r="AP10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ10" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR10" s="1"/>
+      <c r="AT10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX10" s="1"/>
+      <c r="AY10" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ10" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA10" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="XDF10" s="1"/>
       <c r="XDG10" s="1"/>
       <c r="XDH10" s="1"/>
@@ -2091,40 +2403,40 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q11" s="3" t="n">
         <f aca="false">COUNTIF(E11:P11,"P")</f>
@@ -2147,52 +2459,88 @@
         <v>TEA</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y11" s="1" t="n">
         <v>5</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB11" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AD11" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH11" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI11" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AJ11" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AK11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AL11" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AT11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY11" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ11" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA11" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2200,41 +2548,41 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q12" s="3" t="n">
         <f aca="false">COUNTIF(E12:P12,"P")</f>
@@ -2257,43 +2605,74 @@
         <v>TEA</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AB12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE12" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AF12" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="AG12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH12" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AJ12" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="AK12" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN12" s="3"/>
+      <c r="AP12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY12" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ12" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA12" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2301,42 +2680,42 @@
         <v>17</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q13" s="3" t="n">
         <f aca="false">COUNTIF(E13:P13,"P")</f>
@@ -2359,37 +2738,67 @@
         <v>TEA</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AD13" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE13" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AI13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AK13" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY13" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="AZ13" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA13" s="0" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2397,41 +2806,41 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q14" s="3" t="n">
         <f aca="false">COUNTIF(E14:P14,"P")</f>
@@ -2454,156 +2863,185 @@
         <v>TEA</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>7</v>
       </c>
       <c r="Z14" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AB14" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AC14" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="AD14" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE14" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AH14" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AJ14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AK14" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="AK14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AL14" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="XCZ14" s="1"/>
-      <c r="XDA14" s="1"/>
-      <c r="XDB14" s="5"/>
-      <c r="XDC14" s="5"/>
-      <c r="XDD14" s="5"/>
-      <c r="XDE14" s="5"/>
-      <c r="XDF14" s="5"/>
-      <c r="XDG14" s="5"/>
-      <c r="XDH14" s="5"/>
-      <c r="XDI14" s="5"/>
-      <c r="XDJ14" s="5"/>
-      <c r="XDK14" s="5"/>
-      <c r="XDL14" s="5"/>
-      <c r="XDM14" s="5"/>
-      <c r="XDN14" s="5"/>
-      <c r="XDO14" s="5"/>
-      <c r="XDP14" s="5"/>
-      <c r="XDQ14" s="5"/>
-      <c r="XDR14" s="5"/>
-      <c r="XDS14" s="5"/>
-      <c r="XDT14" s="5"/>
-      <c r="XDU14" s="5"/>
-      <c r="XDV14" s="5"/>
-      <c r="XDW14" s="5"/>
-      <c r="XDX14" s="5"/>
-      <c r="XDY14" s="5"/>
-      <c r="XDZ14" s="5"/>
-      <c r="XEA14" s="5"/>
-      <c r="XEB14" s="5"/>
-      <c r="XEC14" s="5"/>
-      <c r="XED14" s="5"/>
-      <c r="XEE14" s="5"/>
-      <c r="XEF14" s="5"/>
-      <c r="XEG14" s="5"/>
-      <c r="XEH14" s="5"/>
-      <c r="XEI14" s="5"/>
-      <c r="XEJ14" s="5"/>
-      <c r="XEK14" s="5"/>
-      <c r="XEL14" s="5"/>
-      <c r="XEM14" s="5"/>
-      <c r="XEN14" s="5"/>
-      <c r="XEO14" s="5"/>
-      <c r="XEP14" s="5"/>
-      <c r="XEQ14" s="5"/>
-      <c r="XER14" s="5"/>
-      <c r="XES14" s="5"/>
-      <c r="XET14" s="5"/>
-      <c r="XEU14" s="5"/>
-      <c r="XEV14" s="5"/>
-      <c r="XEW14" s="5"/>
-      <c r="XEX14" s="5"/>
-      <c r="XEY14" s="5"/>
-      <c r="XEZ14" s="5"/>
-      <c r="XFA14" s="5"/>
-      <c r="XFB14" s="5"/>
-      <c r="XFC14" s="5"/>
-      <c r="XFD14" s="5"/>
+      <c r="AL14" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN14" s="1"/>
+      <c r="AP14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX14" s="1"/>
+      <c r="AY14" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="XDF14" s="1"/>
+      <c r="XDG14" s="1"/>
+      <c r="XDH14" s="1"/>
+      <c r="XDI14" s="1"/>
+      <c r="XDJ14" s="1"/>
+      <c r="XDK14" s="6"/>
+      <c r="XDL14" s="6"/>
+      <c r="XDM14" s="6"/>
+      <c r="XDN14" s="6"/>
+      <c r="XDO14" s="6"/>
+      <c r="XDP14" s="6"/>
+      <c r="XDQ14" s="6"/>
+      <c r="XDR14" s="6"/>
+      <c r="XDS14" s="6"/>
+      <c r="XDT14" s="6"/>
+      <c r="XDU14" s="6"/>
+      <c r="XDV14" s="6"/>
+      <c r="XDW14" s="6"/>
+      <c r="XDX14" s="6"/>
+      <c r="XDY14" s="6"/>
+      <c r="XDZ14" s="6"/>
+      <c r="XEA14" s="6"/>
+      <c r="XEB14" s="6"/>
+      <c r="XEC14" s="6"/>
+      <c r="XED14" s="6"/>
+      <c r="XEE14" s="6"/>
+      <c r="XEF14" s="6"/>
+      <c r="XEG14" s="6"/>
+      <c r="XEH14" s="6"/>
+      <c r="XEI14" s="6"/>
+      <c r="XEJ14" s="6"/>
+      <c r="XEK14" s="6"/>
+      <c r="XEL14" s="6"/>
+      <c r="XEM14" s="6"/>
+      <c r="XEN14" s="6"/>
+      <c r="XEO14" s="6"/>
+      <c r="XEP14" s="6"/>
+      <c r="XEQ14" s="6"/>
+      <c r="XER14" s="6"/>
+      <c r="XES14" s="6"/>
+      <c r="XET14" s="6"/>
+      <c r="XEU14" s="6"/>
+      <c r="XEV14" s="6"/>
+      <c r="XEW14" s="6"/>
+      <c r="XEX14" s="6"/>
+      <c r="XEY14" s="6"/>
+      <c r="XEZ14" s="6"/>
+      <c r="XFA14" s="6"/>
+      <c r="XFB14" s="6"/>
+      <c r="XFC14" s="6"/>
+      <c r="XFD14" s="6"/>
     </row>
-    <row r="15" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="7" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q15" s="3" t="n">
         <f aca="false">COUNTIF(E15:P15,"P")</f>
@@ -2626,45 +3064,75 @@
         <v>TEA</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="X15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y15" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="X15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AA15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB15" s="6" t="n">
+      <c r="AA15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB15" s="7" t="n">
         <v>5</v>
       </c>
       <c r="AD15" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE15" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AF15" s="1"/>
       <c r="AG15" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI15" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="AK15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="XCZ15" s="1"/>
-      <c r="XDA15" s="1"/>
-      <c r="XDB15" s="1"/>
-      <c r="XDC15" s="1"/>
-      <c r="XDD15" s="1"/>
-      <c r="XDE15" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="AM15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN15" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ15" s="1"/>
+      <c r="AR15" s="1"/>
+      <c r="AT15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX15" s="1"/>
+      <c r="AY15" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA15" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="XDF15" s="1"/>
       <c r="XDG15" s="1"/>
       <c r="XDH15" s="1"/>
@@ -2722,40 +3190,40 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="3" t="n">
         <f aca="false">COUNTIF(E16:P16,"P")</f>
@@ -2778,46 +3246,70 @@
         <v>TEA</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W16" s="1"/>
       <c r="X16" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>7</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB16" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AD16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE16" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AF16" s="1"/>
       <c r="AG16" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AH16" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AK16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="XCZ16" s="1"/>
-      <c r="XDA16" s="1"/>
-      <c r="XDB16" s="1"/>
-      <c r="XDC16" s="1"/>
-      <c r="XDD16" s="1"/>
-      <c r="XDE16" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="AM16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ16" s="1"/>
+      <c r="AR16" s="1"/>
+      <c r="AT16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX16" s="1"/>
+      <c r="AY16" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA16" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="XDF16" s="1"/>
       <c r="XDG16" s="1"/>
       <c r="XDH16" s="1"/>
@@ -2875,41 +3367,41 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q17" s="3" t="n">
         <f aca="false">COUNTIF(E17:P17,"P")</f>
@@ -2932,45 +3424,70 @@
         <v>TEA</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>7</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB17" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AD17" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE17" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AH17" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AK17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="XCZ17" s="1"/>
-      <c r="XDA17" s="1"/>
-      <c r="XDB17" s="1"/>
-      <c r="XDC17" s="1"/>
-      <c r="XDD17" s="1"/>
-      <c r="XDE17" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN17" s="1"/>
+      <c r="AP17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ17" s="1"/>
+      <c r="AR17" s="1"/>
+      <c r="AT17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW17" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX17" s="1"/>
+      <c r="AY17" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA17" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="XDF17" s="1"/>
       <c r="XDG17" s="1"/>
       <c r="XDH17" s="1"/>
@@ -3028,41 +3545,41 @@
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="3" t="n">
         <f aca="false">COUNTIF(E18:P18,"P")</f>
@@ -3085,55 +3602,94 @@
         <v>TEA</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB18" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AC18" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AD18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE18" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AF18" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AG18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH18" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI18" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AJ18" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AK18" s="1" t="n">
         <v>10</v>
       </c>
       <c r="AL18" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
+      </c>
+      <c r="AM18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN18" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR18" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY18" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ18" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA18" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3141,43 +3697,43 @@
         <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q19" s="3" t="n">
         <f aca="false">COUNTIF(E19:P19,"P")</f>
@@ -3200,37 +3756,64 @@
         <v>TEA</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD19" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE19" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI19" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AK19" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AM19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY19" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ19" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA19" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3238,40 +3821,40 @@
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q20" s="3" t="n">
         <f aca="false">COUNTIF(E20:P20,"P")</f>
@@ -3294,37 +3877,65 @@
         <v>TEA</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD20" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AG20" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH20" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI20" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AK20" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AM20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN20" s="3"/>
+      <c r="AP20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY20" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ20" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA20" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3332,40 +3943,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q21" s="3" t="n">
         <f aca="false">COUNTIF(E21:P21,"P")</f>
@@ -3388,43 +3999,83 @@
         <v>TEA</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Y21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AB21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD21" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE21" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AH21" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AI21" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AK21" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="AM21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY21" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ21" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA21" s="0" t="n">
+        <v>6</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AT22" s="1" t="n">
+        <f aca="false">COUNTIF(AT2:AT21,"P")</f>
+        <v>17</v>
+      </c>
+      <c r="AU22" s="1" t="n">
+        <f aca="false">COUNTIF(AU2:AU21,"P")</f>
+        <v>19</v>
+      </c>
+      <c r="AY22" s="1" t="n">
+        <f aca="false">COUNTIF(AY2:AY21,"P")</f>
+        <v>19</v>
+      </c>
+    </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>5</v>
@@ -3481,23 +4132,25 @@
         <f aca="false">COUNTIF(AD2:AD22,"P")</f>
         <v>20</v>
       </c>
-      <c r="AE23" s="1"/>
       <c r="AG23" s="1" t="n">
         <f aca="false">COUNTIF(AG2:AG22,"P")</f>
         <v>14</v>
       </c>
-      <c r="AH23" s="1"/>
       <c r="AK23" s="1" t="n">
         <f aca="false">COUNTIF(AK2:AK22,"P")</f>
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="AP23" s="1" t="n">
+        <f aca="false">COUNTIF(AP2:AP22,"P")</f>
+        <v>19</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E24" s="1" t="n">
         <f aca="false">COUNTIF(E3:E17,"M")</f>
@@ -3551,23 +4204,25 @@
         <f aca="false">COUNTIF(AD3:AD17,"M")</f>
         <v>0</v>
       </c>
-      <c r="AE24" s="1"/>
       <c r="AG24" s="1" t="n">
         <f aca="false">COUNTIF(AG3:AG17,"M")</f>
         <v>0</v>
       </c>
-      <c r="AH24" s="1"/>
       <c r="AK24" s="1" t="n">
         <f aca="false">COUNTIF(AK3:AK17,"M")</f>
         <v>0</v>
       </c>
+      <c r="AP24" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP17,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E25" s="1" t="n">
         <f aca="false">COUNTIF(E3:E17,"T")</f>
@@ -3621,14 +4276,16 @@
         <f aca="false">COUNTIF(AD3:AD17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AE25" s="1"/>
       <c r="AG25" s="1" t="n">
         <f aca="false">COUNTIF(AG3:AG17,"T")</f>
         <v>0</v>
       </c>
-      <c r="AH25" s="1"/>
       <c r="AK25" s="1" t="n">
         <f aca="false">COUNTIF(AK3:AK17,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="1" t="n">
+        <f aca="false">COUNTIF(AP3:AP17,"T")</f>
         <v>0</v>
       </c>
     </row>
@@ -3688,15 +4345,17 @@
         <f aca="false">SUM(AD23:AD25)</f>
         <v>20</v>
       </c>
-      <c r="AE26" s="1"/>
       <c r="AG26" s="1" t="n">
         <f aca="false">SUM(AG23:AG25)</f>
         <v>14</v>
       </c>
-      <c r="AH26" s="1"/>
       <c r="AK26" s="1" t="n">
         <f aca="false">SUM(AK23:AK25)</f>
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="AP26" s="1" t="n">
+        <f aca="false">SUM(AP23:AP25)</f>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3779,22 +4438,22 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3802,13 +4461,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>10</v>
@@ -3835,13 +4494,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>7</v>
@@ -3868,13 +4527,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>1</v>
@@ -3901,13 +4560,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>1</v>
@@ -3934,13 +4593,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>9</v>
@@ -3967,13 +4626,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>10</v>
@@ -4000,13 +4659,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>1</v>
@@ -4033,13 +4692,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>8</v>
@@ -4066,13 +4725,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>10</v>
@@ -4099,13 +4758,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>9</v>
@@ -4129,13 +4788,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>9</v>
@@ -4159,13 +4818,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>9</v>
@@ -4189,13 +4848,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>8</v>
@@ -4219,13 +4878,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>8</v>
@@ -4249,13 +4908,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>8</v>
@@ -4279,13 +4938,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>8</v>
@@ -4309,13 +4968,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>9</v>
@@ -4339,13 +4998,13 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>9</v>
@@ -4369,13 +5028,13 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>9</v>
@@ -4399,13 +5058,13 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>9</v>
